--- a/Camp Database.xlsx
+++ b/Camp Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4b2b2d1ad6a78ba7/Desktop/Inq Sem/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="443" documentId="8_{E4654C0D-67C8-484A-B95F-69F2940D7594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{246A0640-2E67-4D24-8071-2B56A093E61C}"/>
+  <xr:revisionPtr revIDLastSave="466" documentId="8_{E4654C0D-67C8-484A-B95F-69F2940D7594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B346DB77-F1F0-4B1E-8D7B-6B69E9EE342A}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{4013957B-741D-4A65-921D-955EA8ACC84A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="134">
   <si>
     <t>Camps Database</t>
   </si>
@@ -340,12 +340,126 @@
   <si>
     <t>https://https//ebookcentral.proquest.com/lib/wpi/detail.action?docID=6357738</t>
   </si>
+  <si>
+    <t>Sevzheldorlag</t>
+  </si>
+  <si>
+    <t>Railway construction (Northern Railway, Kotlas-Konosha-Vorkuta line)</t>
+  </si>
+  <si>
+    <t>Headquartered at Knyazhpogost (now Yemva), Komi ASSR; merged with North Pechora ITL in 1950 to form Pechora ITL</t>
+  </si>
+  <si>
+    <t>Sevzheldorlag - Wikipedia</t>
+  </si>
+  <si>
+    <t>Ozerlag</t>
+  </si>
+  <si>
+    <t>Railway construction (Baikal-Amur Mainline branch lines, Tayshet to Bratsk and Ust-Kut)</t>
+  </si>
+  <si>
+    <t>MVD special camp (Osoblag No. 7) for political prisoners, headquartered near Tayshet, Irkutsk Oblast</t>
+  </si>
+  <si>
+    <t>Ozerlag - Wikipedia</t>
+  </si>
+  <si>
+    <t>Ukhtpechlag</t>
+  </si>
+  <si>
+    <t>Oil and coal mining, plus construction and logging</t>
+  </si>
+  <si>
+    <t>Headquartered at Chibyu (now Ukhta), Komi ASSR; dismantled in 1938 into Vorkutlag, Ukhtizhemlag, Sevzheldorlag, and Ustvymlag</t>
+  </si>
+  <si>
+    <t>Ukhtpechlag - Wikipedia</t>
+  </si>
+  <si>
+    <t>Siblag</t>
+  </si>
+  <si>
+    <t>Forestry, coal mining, and agriculture (diversified across western Siberia)</t>
+  </si>
+  <si>
+    <t>Headquarters relocated repeatedly between Novosibirsk and Mariinsk (Kemerovo Oblast); one of the longest-lasting and most economically diverse Gulag complexes</t>
+  </si>
+  <si>
+    <t>Siblag - Wikidata</t>
+  </si>
+  <si>
+    <t>Forestry and Logging Camps</t>
+  </si>
+  <si>
+    <t>Usollag</t>
+  </si>
+  <si>
+    <t>Logging and timber processing</t>
+  </si>
+  <si>
+    <t>Headquartered in Solikamsk; numerous "lagpunkts" (camp points) across the northern part of then-Molotov (now Perm Krai) Oblast</t>
+  </si>
+  <si>
+    <t>Usollag - Wikipedia</t>
+  </si>
+  <si>
+    <t>Vyatlag</t>
+  </si>
+  <si>
+    <t>Logging and wood processing</t>
+  </si>
+  <si>
+    <t>Headquartered at Lesnoy, Kirov Oblast; over 100,000 prisoners of 80 nationalities passed through 1938-1956; continued as an ordinary penal colony after the Gulag's dissolution</t>
+  </si>
+  <si>
+    <t>Vyatlag - Wikipedia</t>
+  </si>
+  <si>
+    <t>Ustvymlag</t>
+  </si>
+  <si>
+    <t>Logging and forestry</t>
+  </si>
+  <si>
+    <t>Created from a detachment of Ukhtpechlag; headquartered at Ust-Vym, later moved to Vozhayol, Komi ASSR; remained a corrective labor camp until 1960</t>
+  </si>
+  <si>
+    <t>Ustvymlag - Wikipedia</t>
+  </si>
+  <si>
+    <t>Svirlag</t>
+  </si>
+  <si>
+    <t>Logging (timber supplier for Leningrad and its oblast)</t>
+  </si>
+  <si>
+    <t>Headquartered in Lodeynoye Pole, Leningrad Oblast; an estimated 100,000 people were incarcerated there over its existence; included a lagpunkt at the historic Alexander-Svirsky Monastery</t>
+  </si>
+  <si>
+    <t>Svirlag - Wikipedia</t>
+  </si>
+  <si>
+    <t>ALZhIR</t>
+  </si>
+  <si>
+    <t>Forced labor camp for women (the "17th special female detachment"); primarily wives and family members of "traitors to the Motherland"</t>
+  </si>
+  <si>
+    <t>Subcamp of Karlag near Akmol village, Kazakhstan; roughly 18,000 women passed through over its existence; today the site of the ALZhIR Memorial Museum</t>
+  </si>
+  <si>
+    <t>ALZhIR - Wikipedia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI     AI     AI     AI     AI     AI     AI     AI     AI     AI     AI     AI     AI     AI     AI     AI     AI     AI     </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -405,8 +519,51 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -428,6 +585,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -564,11 +727,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -632,11 +797,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -647,20 +816,43 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{84D29363-47E2-4CE2-9A03-1F821D89AF76}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{48D8E7DB-F0F0-43A7-8765-3E1918CB40C3}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -992,10 +1184,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4949C3E9-2849-4A60-A33D-6662058E343A}">
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.46484375" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
@@ -1011,18 +1203,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q2" s="1" t="s">
@@ -1053,7 +1245,7 @@
       <c r="B6" s="3"/>
       <c r="I6" s="4"/>
       <c r="J6" s="2"/>
-      <c r="Q6" s="33" t="s">
+      <c r="Q6" s="25" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1114,7 +1306,7 @@
       <c r="K12" s="8"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="27" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="9" t="s">
@@ -1145,7 +1337,7 @@
       <c r="K13" s="8"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A14" s="30"/>
+      <c r="A14" s="27"/>
       <c r="B14" s="9" t="s">
         <v>19</v>
       </c>
@@ -1174,7 +1366,7 @@
       <c r="K14" s="8"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A15" s="30"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="9" t="s">
         <v>22</v>
       </c>
@@ -1205,7 +1397,7 @@
       <c r="K15" s="8"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A16" s="30"/>
+      <c r="A16" s="27"/>
       <c r="B16" s="9" t="s">
         <v>25</v>
       </c>
@@ -1232,7 +1424,7 @@
       <c r="K16" s="8"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A17" s="31"/>
+      <c r="A17" s="28"/>
       <c r="B17" s="11" t="s">
         <v>29</v>
       </c>
@@ -1263,7 +1455,7 @@
       <c r="K17" s="8"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B18" s="9" t="s">
@@ -1294,7 +1486,7 @@
       <c r="K18" s="8"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A19" s="30"/>
+      <c r="A19" s="27"/>
       <c r="B19" s="15" t="s">
         <v>37</v>
       </c>
@@ -1323,7 +1515,7 @@
       <c r="K19" s="8"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A20" s="30"/>
+      <c r="A20" s="27"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -1336,7 +1528,7 @@
       <c r="K20" s="8"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A21" s="30"/>
+      <c r="A21" s="27"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -1349,7 +1541,7 @@
       <c r="K21" s="8"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A22" s="31"/>
+      <c r="A22" s="28"/>
       <c r="B22" s="17"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -1362,7 +1554,7 @@
       <c r="K22" s="8"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="26" t="s">
         <v>43</v>
       </c>
       <c r="B23" s="18" t="s">
@@ -1391,7 +1583,7 @@
       <c r="K23" s="8"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A24" s="30"/>
+      <c r="A24" s="27"/>
       <c r="B24" s="8" t="s">
         <v>44</v>
       </c>
@@ -1420,7 +1612,7 @@
       <c r="K24" s="8"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A25" s="30"/>
+      <c r="A25" s="27"/>
       <c r="B25" s="8" t="s">
         <v>47</v>
       </c>
@@ -1451,7 +1643,7 @@
       <c r="K25" s="8"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A26" s="30"/>
+      <c r="A26" s="27"/>
       <c r="B26" s="19" t="s">
         <v>50</v>
       </c>
@@ -1480,7 +1672,7 @@
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A27" s="31"/>
+      <c r="A27" s="28"/>
       <c r="B27" s="17" t="s">
         <v>53</v>
       </c>
@@ -1509,7 +1701,7 @@
       <c r="K27" s="8"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="26" t="s">
         <v>56</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -1540,7 +1732,7 @@
       <c r="K28" s="8"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
+      <c r="A29" s="27"/>
       <c r="B29" s="8" t="s">
         <v>61</v>
       </c>
@@ -1569,7 +1761,7 @@
       <c r="K29" s="8"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A30" s="30"/>
+      <c r="A30" s="27"/>
       <c r="B30" s="8" t="s">
         <v>64</v>
       </c>
@@ -1598,7 +1790,7 @@
       <c r="K30" s="8"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A31" s="30"/>
+      <c r="A31" s="27"/>
       <c r="B31" s="19" t="s">
         <v>67</v>
       </c>
@@ -1627,7 +1819,7 @@
       <c r="K31" s="8"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A32" s="31"/>
+      <c r="A32" s="28"/>
       <c r="B32" s="17" t="s">
         <v>71</v>
       </c>
@@ -1656,7 +1848,7 @@
       <c r="K32" s="8"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="26" t="s">
         <v>94</v>
       </c>
       <c r="B33" s="21" t="s">
@@ -1687,7 +1879,7 @@
       <c r="K33" s="8"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A34" s="30"/>
+      <c r="A34" s="27"/>
       <c r="B34" s="8" t="s">
         <v>79</v>
       </c>
@@ -1714,7 +1906,7 @@
       <c r="K34" s="8"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A35" s="30"/>
+      <c r="A35" s="27"/>
       <c r="B35" s="22" t="s">
         <v>83</v>
       </c>
@@ -1741,7 +1933,7 @@
       <c r="K35" s="8"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A36" s="30"/>
+      <c r="A36" s="27"/>
       <c r="B36" s="22" t="s">
         <v>87</v>
       </c>
@@ -1772,7 +1964,7 @@
       <c r="K36" s="8"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A37" s="31"/>
+      <c r="A37" s="28"/>
       <c r="B37" s="23" t="s">
         <v>91</v>
       </c>
@@ -1814,16 +2006,18 @@
       <c r="K38" s="8"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A39" s="5"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="26"/>
+      <c r="A39" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="B39" s="42"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
       <c r="K39" s="8"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.4">
@@ -1840,72 +2034,292 @@
       <c r="K40" s="8"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A41" s="5"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A42" s="5"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
+      <c r="A41" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="35">
+        <v>50.866999999999997</v>
+      </c>
+      <c r="D41" s="35">
+        <v>62.6</v>
+      </c>
+      <c r="E41" s="35">
+        <v>1938</v>
+      </c>
+      <c r="F41" s="35">
+        <v>1950</v>
+      </c>
+      <c r="G41" s="35">
+        <v>84893</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="I41" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="J41" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="K41" s="35"/>
+    </row>
+    <row r="42" spans="1:11" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A42" s="43"/>
+      <c r="B42" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="35">
+        <v>99.772999999999996</v>
+      </c>
+      <c r="D42" s="35">
+        <v>56.127000000000002</v>
+      </c>
+      <c r="E42" s="35">
+        <v>1948</v>
+      </c>
+      <c r="F42" s="35">
+        <v>1958</v>
+      </c>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="I42" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="J42" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="K42" s="35"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A43" s="5"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A44" s="5"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
+      <c r="A43" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C43" s="35">
+        <v>53.7</v>
+      </c>
+      <c r="D43" s="35">
+        <v>63.567</v>
+      </c>
+      <c r="E43" s="35">
+        <v>1931</v>
+      </c>
+      <c r="F43" s="35">
+        <v>1938</v>
+      </c>
+      <c r="G43" s="35">
+        <v>54792</v>
+      </c>
+      <c r="H43" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="I43" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="J43" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="K43" s="35"/>
+    </row>
+    <row r="44" spans="1:11" ht="28.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="43"/>
+      <c r="B44" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" s="35">
+        <v>87.745999999999995</v>
+      </c>
+      <c r="D44" s="35">
+        <v>56.198999999999998</v>
+      </c>
+      <c r="E44" s="35">
+        <v>1929</v>
+      </c>
+      <c r="F44" s="35">
+        <v>1960</v>
+      </c>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="I44" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="J44" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="K44" s="35"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A45" s="5"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
+      <c r="A45" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" s="35">
+        <v>56.77</v>
+      </c>
+      <c r="D45" s="35">
+        <v>59.604999999999997</v>
+      </c>
+      <c r="E45" s="35">
+        <v>1938</v>
+      </c>
+      <c r="F45" s="35">
+        <v>1960</v>
+      </c>
+      <c r="G45" s="35">
+        <v>37000</v>
+      </c>
+      <c r="H45" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="I45" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="J45" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="K45" s="35"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A46" s="43"/>
+      <c r="B46" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" s="35">
+        <v>52.131</v>
+      </c>
+      <c r="D46" s="35">
+        <v>59.781999999999996</v>
+      </c>
+      <c r="E46" s="35">
+        <v>1938</v>
+      </c>
+      <c r="F46" s="35">
+        <v>1956</v>
+      </c>
+      <c r="G46" s="35">
+        <v>28000</v>
+      </c>
+      <c r="H46" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="I46" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="J46" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="K46" s="35"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A47" s="43"/>
+      <c r="B47" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" s="35">
+        <v>50.390999999999998</v>
+      </c>
+      <c r="D47" s="35">
+        <v>62.225999999999999</v>
+      </c>
+      <c r="E47" s="35">
+        <v>1937</v>
+      </c>
+      <c r="F47" s="35">
+        <v>1960</v>
+      </c>
+      <c r="G47" s="35">
+        <v>24245</v>
+      </c>
+      <c r="H47" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="I47" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="J47" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="K47" s="35"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A48" s="43"/>
+      <c r="B48" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48" s="35">
+        <v>33.548000000000002</v>
+      </c>
+      <c r="D48" s="35">
+        <v>60.725999999999999</v>
+      </c>
+      <c r="E48" s="35">
+        <v>1931</v>
+      </c>
+      <c r="F48" s="35">
+        <v>1937</v>
+      </c>
+      <c r="G48" s="35"/>
+      <c r="H48" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="I48" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="J48" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="K48" s="35"/>
+    </row>
+    <row r="49" spans="1:11" ht="26.65" x14ac:dyDescent="0.45">
+      <c r="A49" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" s="33">
+        <v>70.971999999999994</v>
+      </c>
+      <c r="D49" s="33">
+        <v>51.078000000000003</v>
+      </c>
+      <c r="E49" s="33">
+        <v>1938</v>
+      </c>
+      <c r="F49" s="33">
+        <v>1953</v>
+      </c>
+      <c r="G49" s="33">
+        <v>8000</v>
+      </c>
+      <c r="H49" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="I49" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="J49" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="K49" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="10">
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A33:A37"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A13:A17"/>
@@ -1941,6 +2355,15 @@
     <hyperlink ref="J36" r:id="rId24" display="https://en.wikipedia.org/wiki/Solovki_prison_camp" xr:uid="{2B1BF7D7-F73A-4184-A636-8D03555B4320}"/>
     <hyperlink ref="J37" r:id="rId25" display="https://en.wikipedia.org/wiki/Perm-36" xr:uid="{90E0F94A-3BB2-486D-921F-156B7933D55D}"/>
     <hyperlink ref="Q6" r:id="rId26" xr:uid="{47451C0A-B727-4227-BCE8-2F034D73B6DA}"/>
+    <hyperlink ref="J41" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="J42" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="J43" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="J44" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="J45" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="J46" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="J47" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="J48" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="J49" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
